--- a/artfynd/A 45441-2024 artfynd.xlsx
+++ b/artfynd/A 45441-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113273332</v>
+        <v>113273297</v>
       </c>
       <c r="B2" t="n">
-        <v>90723</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576639</v>
+        <v>576690</v>
       </c>
       <c r="R2" t="n">
-        <v>6652368</v>
+        <v>6652412</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -784,12 +784,7 @@
         <v>113273298</v>
       </c>
       <c r="B3" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,12 +890,7 @@
         <v>113273299</v>
       </c>
       <c r="B4" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,37 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113273266</v>
+        <v>113273308</v>
       </c>
       <c r="B5" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576841</v>
+        <v>576793</v>
       </c>
       <c r="R5" t="n">
-        <v>6652447</v>
+        <v>6652437</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1089,11 +1074,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1114,37 +1094,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113273297</v>
+        <v>113273266</v>
       </c>
       <c r="B6" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576690</v>
+        <v>576841</v>
       </c>
       <c r="R6" t="n">
-        <v>6652412</v>
+        <v>6652447</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,15 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113273372</v>
+        <v>113273267</v>
       </c>
       <c r="B7" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576633</v>
+        <v>576913</v>
       </c>
       <c r="R7" t="n">
-        <v>6652405</v>
+        <v>6652462</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1311,6 +1281,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1331,37 +1306,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113273373</v>
+        <v>113273354</v>
       </c>
       <c r="B8" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576729</v>
+        <v>576989</v>
       </c>
       <c r="R8" t="n">
-        <v>6652397</v>
+        <v>6652476</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1417,6 +1387,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1437,15 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113273267</v>
+        <v>113273372</v>
       </c>
       <c r="B9" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1477,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576913</v>
+        <v>576633</v>
       </c>
       <c r="R9" t="n">
-        <v>6652462</v>
+        <v>6652405</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1523,11 +1493,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1548,15 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113273374</v>
+        <v>113273373</v>
       </c>
       <c r="B10" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577005</v>
+        <v>576729</v>
       </c>
       <c r="R10" t="n">
-        <v>6652503</v>
+        <v>6652397</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1654,37 +1614,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113273354</v>
+        <v>113273374</v>
       </c>
       <c r="B11" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576989</v>
+        <v>577005</v>
       </c>
       <c r="R11" t="n">
-        <v>6652476</v>
+        <v>6652503</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1740,11 +1695,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1765,15 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113273308</v>
+        <v>113273332</v>
       </c>
       <c r="B12" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92329</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6040186</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576793</v>
+        <v>576639</v>
       </c>
       <c r="R12" t="n">
-        <v>6652437</v>
+        <v>6652368</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1851,6 +1796,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">

--- a/artfynd/A 45441-2024 artfynd.xlsx
+++ b/artfynd/A 45441-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273297</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273298</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273308</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273266</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273372</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273373</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273332</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1505,6 +1545,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273299</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1611,6 +1656,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273267</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273354</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1818,8 +1873,26 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273374</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>